--- a/resources/templates/notification/Submission template v15.xlsx
+++ b/resources/templates/notification/Submission template v15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nived/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nived/code/senior-accounting-officer-submission-frontend/resources/templates/notification/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="34" documentId="8_{C013D0D2-3629-4339-868B-7567055EB406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1919CBAE-FE83-4506-9F67-DD25068F20F8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{385E0F26-D714-DE43-8BBA-8E250D50B1AF}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17160" xr2:uid="{385E0F26-D714-DE43-8BBA-8E250D50B1AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Submission template" sheetId="1" r:id="rId1"/>
